--- a/97_Mockup/Log_Analysis_Macro.xlsx
+++ b/97_Mockup/Log_Analysis_Macro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIN\Desktop\新しいフォルダー\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio - コピー\97_Mockup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF6F6CC-69BF-4997-B6F3-8A7C515BF99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3067B3-C45B-4D36-B50F-9BC52A60CF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{78629192-825E-4083-940A-C6F0AB98E91E}"/>
   </bookViews>
@@ -17,10 +17,11 @@
     <sheet name="02_抽出結果貼り付け" sheetId="2" r:id="rId2"/>
     <sheet name="03_検索" sheetId="3" r:id="rId3"/>
     <sheet name="04_パラメータ" sheetId="4" r:id="rId4"/>
-    <sheet name="ご説明" sheetId="5" r:id="rId5"/>
+    <sheet name="エラーメッセージ" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_抽出結果貼り付け'!$B$3:$G$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_検索'!$A$1:$H$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
     toを指定します</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="2" shapeId="0" xr:uid="{70DA9179-989F-43DD-9D58-7951A761E7A3}">
+    <comment ref="B24" authorId="2" shapeId="0" xr:uid="{70DA9179-989F-43DD-9D58-7951A761E7A3}">
       <text>
         <t xml:space="preserve">[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
@@ -76,7 +77,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="B18" authorId="3" shapeId="0" xr:uid="{D2DA939B-0C3B-4D00-B458-06EAFF99D17F}">
+    <comment ref="B25" authorId="3" shapeId="0" xr:uid="{D2DA939B-0C3B-4D00-B458-06EAFF99D17F}">
       <text>
         <t xml:space="preserve">[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
@@ -131,14 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="101">
-  <si>
-    <t>ログ解析マクロ</t>
-    <rPh sb="2" eb="4">
-      <t>カイセキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="143">
   <si>
     <t>対象時刻</t>
     <rPh sb="0" eb="2">
@@ -378,9 +372,6 @@
     <t>2027 01-01 15:31:01</t>
   </si>
   <si>
-    <t>2027 01-01 15:32:01</t>
-  </si>
-  <si>
     <t>：○○ファイルリード</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -793,54 +784,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>本制作物は現場で作成したログの解析マクロの見た目のみの再現ファイルとなります。</t>
-    <rPh sb="0" eb="1">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ブツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ゲンバ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カイセキ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>サイゲン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>↓秀丸マクロの実行イメージ</t>
-    <rPh sb="1" eb="3">
-      <t>ヒデマル</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ご説明</t>
-    <rPh sb="1" eb="3">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ループ回数：90</t>
     <rPh sb="3" eb="5">
       <t>カイスウ</t>
@@ -942,95 +885,527 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>なのでボタンを押してもVBAは動きません。</t>
+    <t>To</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">aaa.log(7): </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aaa.log(8):</t>
+  </si>
+  <si>
+    <t>aaa.log(9):</t>
+  </si>
+  <si>
+    <t>aaa.log(10):</t>
+  </si>
+  <si>
+    <t>aaa.log(11):</t>
+  </si>
+  <si>
+    <t>aaa.log(12):</t>
+  </si>
+  <si>
+    <t>2027 01-01 16:32:01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2027 01-01 16:30:01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2027 01-01 16:30:02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2027 01-01 16:30:30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2027 01-01 16:30:XX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2027 01-01 16:31:01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メッセージ モックアップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処理を中止します。</t>
+    <rPh sb="0" eb="2">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在ブック：【ActiveBook】</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在シート：【ActiveWorkSheets】</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除指定行が設定されていません。</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．全行削除を行いますか？</t>
+    <rPh sb="2" eb="4">
+      <t>ゼンギョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクジョ</t>
+    </rPh>
     <rPh sb="7" eb="8">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実際の現場ではVBAは400行規模で作成しましたが、プライベートの時間で作成する時間がないため、仕事で作成した物の見た目のみの共有となります。</t>
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除指定値：【Range型オブジェクト.value】</t>
     <rPh sb="0" eb="2">
-      <t>ジッサイ</t>
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いいえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．E列からG列の削除を行いますか？</t>
+    <rPh sb="3" eb="4">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いいえ：削除キャンセル</t>
+    <rPh sb="4" eb="6">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい：「4:【指定行】」まで削除後、貼り付け位置へオートフォーカス</t>
+    <rPh sb="14" eb="16">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VBEから実行された場合など、配置したボタン以外から実行しアクティブシートが想定シートと違う場合</t>
+    <rPh sb="5" eb="7">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処理を中止する</t>
+    <rPh sb="0" eb="2">
+      <t>ショリ</t>
     </rPh>
     <rPh sb="3" eb="5">
+      <t>チュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除指定行が入力なしの場合</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シテイギョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>念のため、ほかのブックを閉じてください。</t>
+    <rPh sb="0" eb="1">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並べ替え処理を行ってよろしいですか？</t>
+    <rPh sb="0" eb="1">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>****************************************************************************</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※パフォーマンスを上げる場合は、ローカルでの実行を推奨いたします。</t>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>スイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並べ替えボタン押下時の確認画面。</t>
+    <rPh sb="0" eb="1">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VBAはアクティブシートに影響を与える可能性のある言語なので他ブックを閉じることを推奨。</t>
+    <rPh sb="13" eb="15">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>スイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現場で作成したツールのエラーハンドリングの一例です。</t>
+    <rPh sb="0" eb="2">
       <t>ゲンバ</t>
     </rPh>
-    <rPh sb="14" eb="15">
-      <t>ギョウ</t>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イチレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実行中のシートが、【Worksheetsオブジェクト.name】シートではありません。</t>
+    <rPh sb="0" eb="3">
+      <t>ジッコウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間的な都合で一部抜粋になります。</t>
+    <rPh sb="0" eb="3">
+      <t>ジカンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツゴウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バッスイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイル作成処理で例外が発生しました。</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;例外メッセージ&gt;</t>
+    <rPh sb="1" eb="3">
+      <t>レイガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【例外オブジェクト】</t>
+    <rPh sb="1" eb="3">
+      <t>レイガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイルが排他制御されていないか、および作成先の権限を確認してください。</t>
+    <rPh sb="5" eb="7">
+      <t>ハイタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秀丸マクロ作成時のエラーメッセージ</t>
+    <rPh sb="0" eb="2">
+      <t>ヒデマル</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【Worksheetsオブジェクト.name】を確認してください。</t>
+    <rPh sb="24" eb="26">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログ解析マクロ（モックアップ）</t>
+    <rPh sb="2" eb="4">
+      <t>カイセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">実行時 シートチェック </t>
+    <rPh sb="0" eb="2">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セルの値クリア ボタン押下時</t>
+    <rPh sb="3" eb="4">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セルの値クリア ボタン押下時 いいえ選択時</t>
+    <rPh sb="3" eb="4">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい：セル範囲削除後に削除対象範囲をオートフォーカス</t>
+    <rPh sb="5" eb="7">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイショウ</t>
     </rPh>
     <rPh sb="15" eb="17">
-      <t>キボ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並べ替えボタン押下時</t>
+    <rPh sb="0" eb="1">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>秀丸マクロ作成時</t>
+    <rPh sb="0" eb="2">
+      <t>ヒデマル</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>サクセイ</t>
     </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>シゴト</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>キョウユウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>VBAや正規表現、ログの収集など詳細な技術の説明が必要の場合は面談でのご説明とさせていただければ幸いです。</t>
-    <rPh sb="4" eb="6">
-      <t>セイキ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヒョウゲン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シュウシュウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ギジュツ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>メンダン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>サイワ</t>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1039,7 +1414,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1088,19 +1463,22 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1122,12 +1500,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1187,13 +1565,99 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1209,13 +1673,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
@@ -1224,37 +1685,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
@@ -1266,6 +1709,15 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1275,16 +1727,58 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1397,13 +1891,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>638175</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>219075</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>7</xdr:col>
           <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1460,6 +1954,200 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="吹き出し: 角を丸めた四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA4D0BCA-0BAC-EC9D-CC16-C26353881823}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7429500" y="1581150"/>
+          <a:ext cx="2257425" cy="2152650"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -77795"/>
+            <a:gd name="adj2" fmla="val 36859"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1)C24</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>にログを</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Grep</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>するための、正規表現が作成されます。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>2)c38:c42</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>に</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Grep</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>結果の時刻フォーマットを一つに統一するための正規表現を使用した置換を行うための秀丸マクロが作成されます。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="吹き出し: 角を丸めた四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79751916-8185-46E0-8554-686E572D7C25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8010525" y="6324599"/>
+          <a:ext cx="2257425" cy="1714501"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -77795"/>
+            <a:gd name="adj2" fmla="val 36859"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>作成パスに</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>c38:c42</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>の内容を操作説明コメントとともにファイルを出力します。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>2)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>作成ファイル名はハードコーディングしたデフォルトのファイル名。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1603,97 +2291,200 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1114424</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>172458</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>86103</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1447799</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="吹き出し: 角を丸めた四角形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AC8CEA2-E828-4ED4-B555-E413DC92808F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18287DAA-E28D-4AD5-819B-04773CE4C8C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="704850" y="3333750"/>
-          <a:ext cx="7220958" cy="2705478"/>
+          <a:off x="8429624" y="1162049"/>
+          <a:ext cx="2486025" cy="3057525"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -73624"/>
+            <a:gd name="adj2" fmla="val -85671"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
         </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:alpha val="20000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>439207</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>95601</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7A83604-9E5E-4E5E-B61B-65BDD7985846}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="619125" y="5676900"/>
-          <a:ext cx="7573432" cy="2514951"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1)C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>列を第一優先、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>列を第二優先で昇順にソート</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2)D</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>列の内容が</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>03</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>シートの単語にヒットした場合、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>列にラベルを設定する</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3)E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>のハイフン（検索ヒットなし）を除き、自動フィルタリング</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2028,11 +2819,11 @@
   <threadedComment ref="D11" dT="2026-01-19T13:29:18.99" personId="{9832D48C-5CB3-4915-9C87-D31F530CC99B}" id="{5E217C0D-1D55-4E96-A81C-157A4DC4F5E7}">
     <text>toを指定します</text>
   </threadedComment>
-  <threadedComment ref="B17" dT="2026-01-19T13:28:12.36" personId="{9832D48C-5CB3-4915-9C87-D31F530CC99B}" id="{70DA9179-989F-43DD-9D58-7951A761E7A3}">
+  <threadedComment ref="B24" dT="2026-01-19T13:28:12.36" personId="{9832D48C-5CB3-4915-9C87-D31F530CC99B}" id="{70DA9179-989F-43DD-9D58-7951A761E7A3}">
     <text xml:space="preserve">正規表現作成ボタンを押すと自動で正規表現が作成されます
 </text>
   </threadedComment>
-  <threadedComment ref="B18" dT="2026-01-19T13:28:58.79" personId="{9832D48C-5CB3-4915-9C87-D31F530CC99B}" id="{D2DA939B-0C3B-4D00-B458-06EAFF99D17F}">
+  <threadedComment ref="B25" dT="2026-01-19T13:28:58.79" personId="{9832D48C-5CB3-4915-9C87-D31F530CC99B}" id="{D2DA939B-0C3B-4D00-B458-06EAFF99D17F}">
     <text xml:space="preserve">ブック起動時またはマクロ有効時に前回使用正規表現がバックアップされます
 </text>
   </threadedComment>
@@ -2061,7 +2852,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F4E0EA-36C9-4763-B92F-BBE310F50508}">
-  <dimension ref="B2:O38"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:O59"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2069,327 +2863,440 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="33" x14ac:dyDescent="0.4">
-      <c r="B2" s="12" t="s">
-        <v>0</v>
+      <c r="B2" s="9" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B6" s="14" t="s">
-        <v>97</v>
+      <c r="B6" s="10" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B7" s="7"/>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B8" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B9" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B10" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B11" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B12" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B13" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="15" spans="2:4" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="2:4" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="17" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B22" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B24" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B15" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B17" s="6" t="s">
+      <c r="C24" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="13"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B25" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="17"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="C25" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="19"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B26" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="23"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B19" s="6" t="s">
+      <c r="C26" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="22"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B27" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="26"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B20" s="6" t="s">
+      <c r="C27" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="22"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+    </row>
+    <row r="29" spans="2:15" hidden="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+    </row>
+    <row r="30" spans="2:15" hidden="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+    </row>
+    <row r="31" spans="2:15" hidden="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+    </row>
+    <row r="32" spans="2:15" hidden="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+    </row>
+    <row r="33" spans="2:15" hidden="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+    </row>
+    <row r="34" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="35" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="26"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B23" s="2" t="s">
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B38" s="25" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B25" s="6" t="s">
+      <c r="C38" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="13"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B39" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="17"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="16"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B40" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C40" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="16"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B41" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="16"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B42" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="16"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B44" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="20"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B27" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="20"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B28" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="20"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="20"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B31" s="6" t="s">
+      <c r="D44" s="16"/>
+    </row>
+    <row r="46" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="47" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="48" spans="2:15" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="49" spans="2:3" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="50" spans="2:3" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="51" spans="2:3" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="52" spans="2:3" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B55" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="20"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B34" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B35" t="s">
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B58" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>93</v>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B59" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2408,15 +3315,16 @@
       <formula1>"01,02,03,04,05,06,07,08,09,10,11,12,13,14,15,16,17,18,19,20,21,22,23"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1026" r:id="rId3" name="Button 2">
+            <control shapeId="1026" r:id="rId4" name="Button 2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ボタン2_Click">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -2438,19 +3346,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1027" r:id="rId4" name="Button 3">
+            <control shapeId="1027" r:id="rId5" name="Button 3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ボタン2_Click">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>638175</xdr:colOff>
-                    <xdr:row>29</xdr:row>
+                    <xdr:row>42</xdr:row>
                     <xdr:rowOff>219075</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>7</xdr:col>
                     <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>31</xdr:row>
+                    <xdr:row>44</xdr:row>
                     <xdr:rowOff>76200</xdr:rowOff>
                   </to>
                 </anchor>
@@ -2466,6 +3374,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C143EFB0-F4E1-4B88-8FB7-76099DCBB5DA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:T41"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -2482,726 +3393,717 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="27"/>
-      <c r="I1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B4" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B4" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B5" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="29"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B7" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B7" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
-        <v>59</v>
+      <c r="G9" s="29" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B10" s="1" t="s">
-        <v>70</v>
+      <c r="B10" s="24" t="s">
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>70</v>
+      <c r="G10" s="29" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B11" s="1" t="s">
-        <v>70</v>
+      <c r="B11" s="24" t="s">
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G11" s="29"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B12" s="1" t="s">
-        <v>70</v>
+      <c r="B12" s="24" t="s">
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G12" s="29"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>70</v>
+      <c r="B13" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>104</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G13" s="29"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B14" s="1" t="s">
-        <v>70</v>
+      <c r="B14" s="24" t="s">
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="G14" s="29"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B15" s="1" t="s">
-        <v>70</v>
+      <c r="B15" s="24" t="s">
+        <v>99</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>70</v>
+      <c r="G15" s="29" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1" t="s">
-        <v>70</v>
+      <c r="G16" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
-        <v>70</v>
+      <c r="G17" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="1" t="s">
-        <v>70</v>
+      <c r="G18" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="1" t="s">
-        <v>70</v>
+      <c r="G19" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
-        <v>70</v>
+      <c r="G20" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
-        <v>70</v>
+      <c r="G21" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
-        <v>70</v>
+      <c r="G22" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="1" t="s">
-        <v>70</v>
+      <c r="G23" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="1" t="s">
-        <v>70</v>
+      <c r="G24" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
-        <v>70</v>
+      <c r="G25" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
-        <v>70</v>
+      <c r="G26" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1"/>
-      <c r="G27" s="1" t="s">
-        <v>70</v>
+      <c r="G27" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="1" t="s">
-        <v>70</v>
+      <c r="G28" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="1" t="s">
-        <v>70</v>
+      <c r="G29" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>70</v>
+      <c r="G30" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>70</v>
+      <c r="G31" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
-        <v>70</v>
+      <c r="G32" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B33" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>70</v>
+      <c r="G33" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="1" t="s">
-        <v>70</v>
+      <c r="G34" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
-        <v>70</v>
+      <c r="G35" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1" t="s">
-        <v>70</v>
+      <c r="G36" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
-        <v>70</v>
+      <c r="G37" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>70</v>
+      <c r="G38" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F39" s="1"/>
-      <c r="G39" s="1" t="s">
-        <v>70</v>
+      <c r="G39" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F40" s="1"/>
-      <c r="G40" s="1" t="s">
-        <v>70</v>
+      <c r="G40" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B41" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F41" s="1"/>
-      <c r="G41" s="1" t="s">
-        <v>70</v>
+      <c r="G41" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B3:G3" xr:uid="{C143EFB0-F4E1-4B88-8FB7-76099DCBB5DA}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup scale="57" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2051" r:id="rId3" name="Button 3">
+            <control shapeId="2051" r:id="rId4" name="Button 3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ボタン2_Click">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3223,7 +4125,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2052" r:id="rId4" name="Button 4">
+            <control shapeId="2052" r:id="rId5" name="Button 4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ボタン2_Click">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3251,6 +4153,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC64D4F7-52E2-4C6D-8153-F76B3339D2AA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:T93"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3266,1196 +4171,1196 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B1" s="27" t="s">
-        <v>87</v>
+      <c r="B1" s="23" t="s">
+        <v>82</v>
       </c>
       <c r="H1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B3" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B3" s="6" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B4" s="24">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B5" s="5">
+      <c r="B5" s="24">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B6" s="5">
+      <c r="B6" s="24">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B7" s="5">
+      <c r="B7" s="24">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B8" s="5">
+      <c r="B8" s="24">
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B9" s="5">
+      <c r="B9" s="24">
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B10" s="5">
+      <c r="B10" s="24">
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B11" s="5">
+      <c r="B11" s="24">
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B12" s="5">
+      <c r="B12" s="24">
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B13" s="5">
+      <c r="B13" s="24">
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B14" s="5">
+      <c r="B14" s="24">
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B15" s="5">
+      <c r="B15" s="24">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B16" s="5">
+      <c r="B16" s="24">
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B17" s="5">
+      <c r="B17" s="24">
         <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="5">
+      <c r="B18" s="24">
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B19" s="5">
+      <c r="B19" s="24">
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="5">
+      <c r="B20" s="24">
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="5">
+      <c r="B21" s="24">
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="5">
+      <c r="B22" s="24">
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="5">
+      <c r="B23" s="24">
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="5">
+      <c r="B24" s="24">
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="5">
+      <c r="B25" s="24">
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B26" s="5">
+      <c r="B26" s="24">
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B27" s="5">
+      <c r="B27" s="24">
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B28" s="5">
+      <c r="B28" s="24">
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B29" s="5">
+      <c r="B29" s="24">
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B30" s="5">
+      <c r="B30" s="24">
         <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B31" s="5">
+      <c r="B31" s="24">
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B32" s="5">
+      <c r="B32" s="24">
         <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B33" s="5">
+      <c r="B33" s="24">
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B34" s="5">
+      <c r="B34" s="24">
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B35" s="5">
+      <c r="B35" s="24">
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B36" s="5">
+      <c r="B36" s="24">
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B37" s="5">
+      <c r="B37" s="24">
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B38" s="5">
+      <c r="B38" s="24">
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B39" s="5">
+      <c r="B39" s="24">
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B40" s="5">
+      <c r="B40" s="24">
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B41" s="5">
+      <c r="B41" s="24">
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B42" s="5">
+      <c r="B42" s="24">
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B43" s="5">
+      <c r="B43" s="24">
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B44" s="5">
+      <c r="B44" s="24">
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B45" s="5">
+      <c r="B45" s="24">
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B46" s="5">
+      <c r="B46" s="24">
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B47" s="5">
+      <c r="B47" s="24">
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B48" s="5">
+      <c r="B48" s="24">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B49" s="5">
+      <c r="B49" s="24">
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B50" s="5">
+      <c r="B50" s="24">
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B51" s="5">
+      <c r="B51" s="24">
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B52" s="5">
+      <c r="B52" s="24">
         <v>49</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B53" s="5">
+      <c r="B53" s="24">
         <v>50</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B54" s="5">
+      <c r="B54" s="24">
         <v>51</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B55" s="5">
+      <c r="B55" s="24">
         <v>52</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B56" s="5">
+      <c r="B56" s="24">
         <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B57" s="5">
+      <c r="B57" s="24">
         <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B58" s="5">
+      <c r="B58" s="24">
         <v>55</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B59" s="5">
+      <c r="B59" s="24">
         <v>56</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B60" s="5">
+      <c r="B60" s="24">
         <v>57</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B61" s="5">
+      <c r="B61" s="24">
         <v>58</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="5">
+      <c r="B62" s="24">
         <v>59</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B63" s="5">
+      <c r="B63" s="24">
         <v>60</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B64" s="5">
+      <c r="B64" s="24">
         <v>61</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B65" s="5">
+      <c r="B65" s="24">
         <v>62</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B66" s="5">
+      <c r="B66" s="24">
         <v>63</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B67" s="5">
+      <c r="B67" s="24">
         <v>64</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B68" s="5">
+      <c r="B68" s="24">
         <v>65</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B69" s="5">
+      <c r="B69" s="24">
         <v>66</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B70" s="5">
+      <c r="B70" s="24">
         <v>67</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B71" s="5">
+      <c r="B71" s="24">
         <v>68</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B72" s="5">
+      <c r="B72" s="24">
         <v>69</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B73" s="5">
+      <c r="B73" s="24">
         <v>70</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B74" s="5">
+      <c r="B74" s="24">
         <v>71</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B75" s="5">
+      <c r="B75" s="24">
         <v>72</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B76" s="5">
+      <c r="B76" s="24">
         <v>73</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B77" s="5">
+      <c r="B77" s="24">
         <v>74</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B78" s="5">
+      <c r="B78" s="24">
         <v>75</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B79" s="5">
+      <c r="B79" s="24">
         <v>76</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B80" s="5">
+      <c r="B80" s="24">
         <v>77</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B81" s="5">
+      <c r="B81" s="24">
         <v>78</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B82" s="5">
+      <c r="B82" s="24">
         <v>79</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B83" s="5">
+      <c r="B83" s="24">
         <v>80</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B84" s="5">
+      <c r="B84" s="24">
         <v>81</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B85" s="5">
+      <c r="B85" s="24">
         <v>82</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B86" s="5">
+      <c r="B86" s="24">
         <v>83</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B87" s="5">
+      <c r="B87" s="24">
         <v>84</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B88" s="5">
+      <c r="B88" s="24">
         <v>85</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B89" s="5">
+      <c r="B89" s="24">
         <v>86</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B90" s="5">
+      <c r="B90" s="24">
         <v>87</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B91" s="5">
+      <c r="B91" s="24">
         <v>88</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B92" s="5">
+      <c r="B92" s="24">
         <v>89</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B93" s="5">
+      <c r="B93" s="24">
         <v>90</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -4463,11 +5368,15 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="69" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91BE9300-507B-474B-810F-54F498494ADC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:E14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4478,87 +5387,87 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>72</v>
+      <c r="B2" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
@@ -4605,59 +5514,776 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;P / &amp;N ページ</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C65A93-0017-4338-A0F3-70A6FCB8C9AC}">
-  <dimension ref="B2:B14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62CE467-596B-4B58-9B9A-88B0A91A5915}">
+  <dimension ref="B1:L82"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="11.75" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B2" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="30">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:12" ht="30" x14ac:dyDescent="0.4">
+      <c r="B1" s="36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B8" s="29"/>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="39"/>
+      <c r="L8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="32"/>
+      <c r="L9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="32"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B11" s="30"/>
+      <c r="C11" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="32"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="32"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B16" s="33"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="35"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B22" s="37"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="39"/>
+      <c r="L22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="32"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B24" s="30"/>
+      <c r="C24" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="32"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B25" s="30"/>
+      <c r="C25" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="32"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B26" s="30"/>
+      <c r="C26" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="32"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="32"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="32"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="32"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B30" s="33"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="35"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B35" s="37"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="39"/>
+      <c r="L35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="32"/>
+      <c r="L36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B37" s="30"/>
+      <c r="C37" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="32"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B38" s="30"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="32"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B39" s="30"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="32"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B40" s="30"/>
+      <c r="C40" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="32"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="32"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B42" s="30"/>
+      <c r="C42" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="39"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="I42" s="39"/>
+      <c r="J42" s="32"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B43" s="33"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="35"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B47" s="37"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="39"/>
+      <c r="L47" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B48" s="30"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="32"/>
+      <c r="L48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B49" s="30"/>
+      <c r="C49" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="32"/>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B50" s="30"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="32"/>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B51" s="30"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="32"/>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B52" s="30"/>
+      <c r="C52" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="32"/>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B53" s="30"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="32"/>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B54" s="30"/>
+      <c r="C54" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="39"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="I54" s="39"/>
+      <c r="J54" s="32"/>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B55" s="33"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="35"/>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B58" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B59" s="37"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="39"/>
+      <c r="L59" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B60" s="30"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="31"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="32"/>
+      <c r="L60" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B61" s="30"/>
+      <c r="C61" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="32"/>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B62" s="30"/>
+      <c r="C62" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D62" s="31"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="31"/>
+      <c r="I62" s="31"/>
+      <c r="J62" s="32"/>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B63" s="30"/>
+      <c r="C63" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="31"/>
+      <c r="I63" s="31"/>
+      <c r="J63" s="32"/>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B64" s="30"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="32"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B65" s="30"/>
+      <c r="C65" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="31"/>
+      <c r="I65" s="31"/>
+      <c r="J65" s="32"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B66" s="30"/>
+      <c r="C66" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="32"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B67" s="30"/>
+      <c r="C67" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="32"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B68" s="30"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="31"/>
+      <c r="I68" s="31"/>
+      <c r="J68" s="32"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B69" s="30"/>
+      <c r="C69" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D69" s="39"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="I69" s="39"/>
+      <c r="J69" s="32"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B70" s="33"/>
+      <c r="C70" s="34"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="34"/>
+      <c r="F70" s="34"/>
+      <c r="G70" s="34"/>
+      <c r="H70" s="34"/>
+      <c r="I70" s="34"/>
+      <c r="J70" s="35"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B73" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B74" s="37"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="39"/>
+      <c r="L74" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B75" s="30"/>
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+      <c r="E75" s="31"/>
+      <c r="F75" s="31"/>
+      <c r="G75" s="31"/>
+      <c r="H75" s="31"/>
+      <c r="I75" s="31"/>
+      <c r="J75" s="32"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B76" s="30"/>
+      <c r="C76" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D76" s="31"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="31"/>
+      <c r="J76" s="32"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B77" s="30"/>
+      <c r="C77" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D77" s="31"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
+      <c r="J77" s="32"/>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B78" s="30"/>
+      <c r="C78" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="32"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B79" s="30"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
+      <c r="J79" s="32"/>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B80" s="30"/>
+      <c r="C80" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="31"/>
+      <c r="I80" s="31"/>
+      <c r="J80" s="32"/>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B81" s="30"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+      <c r="H81" s="31"/>
+      <c r="I81" s="31"/>
+      <c r="J81" s="32"/>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B82" s="33"/>
+      <c r="C82" s="34"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="34"/>
+      <c r="H82" s="34"/>
+      <c r="I82" s="34"/>
+      <c r="J82" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>